--- a/importaciones_productos/ME607409 registro productos.xlsx
+++ b/importaciones_productos/ME607409 registro productos.xlsx
@@ -500,7 +500,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>PILRECGPUn</t>
+          <t>PILAAA</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
